--- a/data/trans_dic/IP26C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 16,04</t>
+          <t>3,58; 16,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 20,31</t>
+          <t>5,73; 19,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 23,36</t>
+          <t>7,39; 23,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 18,66</t>
+          <t>4,95; 18,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 19,99</t>
+          <t>5,99; 20,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,74</t>
+          <t>1,12; 11,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,87</t>
+          <t>0,73; 9,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 14,58</t>
+          <t>4,96; 14,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,91</t>
+          <t>7,01; 17,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 14,28</t>
+          <t>5,26; 13,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,12</t>
+          <t>0,5; 5,18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 16,07</t>
+          <t>5,86; 15,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 11,77</t>
+          <t>2,43; 10,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 17,84</t>
+          <t>6,86; 17,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,5</t>
+          <t>1,21; 7,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 12,08</t>
+          <t>4,18; 12,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 9,73</t>
+          <t>2,58; 10,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,89; 18,64</t>
+          <t>7,82; 18,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 9,58</t>
+          <t>0,88; 9,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 12,98</t>
+          <t>6,19; 12,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,95</t>
+          <t>3,61; 8,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,94</t>
+          <t>8,85; 16,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,73</t>
+          <t>1,7; 7,0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 21,58</t>
+          <t>7,19; 20,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 23,08</t>
+          <t>7,67; 22,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 13,89</t>
+          <t>3,06; 13,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 18,67</t>
+          <t>4,81; 18,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 21,51</t>
+          <t>8,09; 21,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,89; 25,68</t>
+          <t>11,27; 26,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 15,5</t>
+          <t>4,02; 14,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 16,68</t>
+          <t>3,34; 15,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,16; 18,55</t>
+          <t>9,03; 18,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 21,09</t>
+          <t>11,43; 21,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 12,21</t>
+          <t>4,78; 12,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 14,27</t>
+          <t>5,27; 13,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,49; 29,36</t>
+          <t>13,86; 28,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,65</t>
+          <t>0,86; 8,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 15,07</t>
+          <t>4,42; 15,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 15,37</t>
+          <t>3,88; 15,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 20,08</t>
+          <t>7,71; 19,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,13</t>
+          <t>0,79; 7,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 20,64</t>
+          <t>7,87; 20,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 16,24</t>
+          <t>1,78; 16,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 22,34</t>
+          <t>12,37; 22,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,21</t>
+          <t>1,57; 6,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,61; 16,02</t>
+          <t>7,32; 15,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 13,33</t>
+          <t>3,84; 12,67</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 13,24</t>
+          <t>1,55; 13,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 15,87</t>
+          <t>1,58; 15,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,17</t>
+          <t>0,0; 11,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,63</t>
+          <t>0,0; 7,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,89</t>
+          <t>1,4; 12,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,53</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 18,02</t>
+          <t>4,33; 18,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,81</t>
+          <t>0,78; 7,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 11,46</t>
+          <t>2,43; 11,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 11,5</t>
+          <t>3,23; 11,81</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,55; 27,24</t>
+          <t>10,87; 27,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,74; 31,83</t>
+          <t>12,75; 30,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 7,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,03; 47,14</t>
+          <t>25,08; 46,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,87; 27,3</t>
+          <t>11,63; 27,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,84; 32,4</t>
+          <t>15,24; 33,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,53</t>
+          <t>0,0; 8,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,84; 42,65</t>
+          <t>23,28; 42,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,11; 24,14</t>
+          <t>13,24; 24,79</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,13; 28,49</t>
+          <t>16,16; 28,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,12</t>
+          <t>0,56; 5,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,82; 41,47</t>
+          <t>27,07; 42,77</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,98; 17,01</t>
+          <t>7,78; 17,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,05; 23,02</t>
+          <t>12,24; 22,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 14,65</t>
+          <t>5,43; 13,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,81</t>
+          <t>3,84; 11,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 14,03</t>
+          <t>5,67; 13,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,09; 21,04</t>
+          <t>11,22; 21,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 16,22</t>
+          <t>7,2; 16,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 14,61</t>
+          <t>5,86; 14,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,62; 14,09</t>
+          <t>7,71; 13,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,92; 20,11</t>
+          <t>12,93; 20,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,29; 13,34</t>
+          <t>7,5; 13,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 11,71</t>
+          <t>6,08; 11,59</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,32</t>
+          <t>4,38; 11,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,87; 10,62</t>
+          <t>4,36; 11,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,61; 16,57</t>
+          <t>8,79; 16,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,21; 17,93</t>
+          <t>8,12; 18,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,79</t>
+          <t>3,8; 9,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,16; 11,85</t>
+          <t>5,48; 12,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,58; 15,24</t>
+          <t>7,4; 15,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,21; 24,58</t>
+          <t>12,88; 23,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,67</t>
+          <t>4,98; 9,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,46</t>
+          <t>5,48; 10,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,97; 14,81</t>
+          <t>9,13; 14,86</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,92; 18,94</t>
+          <t>11,97; 19,63</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,7; 13,84</t>
+          <t>9,61; 13,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,34</t>
+          <t>8,8; 12,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,59; 11,28</t>
+          <t>7,62; 11,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,95</t>
+          <t>7,18; 11,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,78; 11,22</t>
+          <t>7,83; 11,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,99</t>
+          <t>9,13; 12,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,15</t>
+          <t>7,65; 11,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,86; 12,95</t>
+          <t>8,86; 12,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,31; 11,82</t>
+          <t>9,07; 11,87</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,41; 12,07</t>
+          <t>9,28; 12,02</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,68</t>
+          <t>8,15; 10,63</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,56</t>
+          <t>8,72; 11,66</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4354</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6406</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8120</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5910</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7068</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2910</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2446</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>10264</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13474</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11031</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1833; 8598</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3245; 11130</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4240; 13325</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3304</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2910; 11073</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3810; 13009</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>724; 7208</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>577; 7434</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5449; 15674</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8420; 20447</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6413; 16368</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>762; 7904</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10537</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6078</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4584</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8068</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6177</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13856</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4784</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>18605</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>12255</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>25634</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>9368</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5951; 15793</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2513; 10808</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7007; 17946</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1520; 9341</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4543; 13544</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2814; 11490</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8579; 20545</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1119; 12208</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>13025; 25822</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7687; 18922</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>18746; 34172</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4298; 17716</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8547</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9472</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6026</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9388</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12634</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5794</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5293</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>17935</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22106</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10262</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>11319</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4857; 13864</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5176; 15220</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2001; 8917</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2803; 10652</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5639; 15011</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8030; 18769</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2808; 10140</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2242; 10097</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>12391; 25432</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>15865; 29403</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6463; 16502</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6608; 17105</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15949</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6846</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5849</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2413</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10701</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>25894</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5077</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>17546</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>11019</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>10379; 21698</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>655; 6687</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3339; 11627</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2723; 10561</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6052; 15687</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>639; 6036</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6333; 16229</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1392; 12942</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>18970; 34711</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2462; 9566</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>11420; 24510</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5695; 18790</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3978</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2662</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5010</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>638; 5391</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>694; 6914</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4006</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3236</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>652; 5839</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2843</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1765; 7571</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>658; 6542</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2200; 10165</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3308</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2432; 8885</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>10300</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11471</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>16518</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>10769</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>13852</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>18302</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>21068</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>25323</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>34821</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>6091; 15623</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>7138; 16841</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4183</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11579; 21538</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>6870; 16064</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>9183; 20092</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4795</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>13080; 23887</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>15238; 28537</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>18782; 32971</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>633; 5800</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>27708; 43778</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>15308</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>23269</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12515</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9064</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>22233</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>15823</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>14634</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>27939</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>45502</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>28338</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>23698</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>10001; 21869</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>16863; 31380</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>7385; 18809</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>4782; 14760</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>7691; 18925</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>16135; 30782</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10186; 22812</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>9124; 23256</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>20372; 36915</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>36418; 56607</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>20815; 37457</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>17023; 32464</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>11916</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>20433</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>15977</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>10224</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>14251</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>18260</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>28190</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>22140</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>25588</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>38693</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>44167</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>6909; 17862</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>7058; 17994</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>14298; 27590</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>10693; 23979</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>6184; 16195</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>9269; 20814</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>12516; 26027</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>20194; 36120</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>15978; 30525</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>18163; 34253</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>30291; 49293</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>34528; 56629</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>78908</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>73218</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>65539</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>59719</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>67600</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>81283</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>146507</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>154501</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>134191</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>142515</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>65248; 92607</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>61927; 87534</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>53124; 78190</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>47668; 74045</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>56136; 80860</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>67988; 96061</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>56504; 83849</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>67496; 98738</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>126605; 165722</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>134359; 174051</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>116934; 152569</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>124334; 166277</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP26C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 16,79</t>
+          <t>3,67; 15,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 19,67</t>
+          <t>5,44; 19,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 23,23</t>
+          <t>8,23; 23,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 18,84</t>
+          <t>5,05; 19,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 20,47</t>
+          <t>5,64; 19,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 11,18</t>
+          <t>1,07; 10,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 9,37</t>
+          <t>0,76; 8,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 14,25</t>
+          <t>5,4; 14,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 17,02</t>
+          <t>6,9; 16,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 13,44</t>
+          <t>5,41; 14,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,18</t>
+          <t>0,47; 5,13</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 15,55</t>
+          <t>6,19; 15,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 10,45</t>
+          <t>2,57; 10,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 17,57</t>
+          <t>7,17; 17,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,43</t>
+          <t>1,08; 7,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 12,45</t>
+          <t>4,23; 12,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,52</t>
+          <t>2,93; 10,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,82; 18,74</t>
+          <t>8,14; 18,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,57</t>
+          <t>0,86; 9,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 12,28</t>
+          <t>5,89; 12,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,9</t>
+          <t>3,39; 8,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,85; 16,14</t>
+          <t>8,97; 16,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,0</t>
+          <t>1,8; 6,91</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 20,51</t>
+          <t>6,56; 20,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 22,55</t>
+          <t>8,41; 22,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 13,62</t>
+          <t>2,37; 13,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 18,28</t>
+          <t>5,06; 18,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,09; 21,54</t>
+          <t>8,03; 20,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,27; 26,34</t>
+          <t>11,73; 26,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 14,5</t>
+          <t>4,01; 15,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 15,03</t>
+          <t>2,97; 16,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,03; 18,53</t>
+          <t>9,04; 17,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,43; 21,19</t>
+          <t>11,31; 21,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 12,19</t>
+          <t>4,44; 12,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 13,64</t>
+          <t>5,18; 14,39</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,86; 28,98</t>
+          <t>14,78; 29,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,76</t>
+          <t>1,03; 9,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 15,38</t>
+          <t>4,9; 16,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 15,06</t>
+          <t>4,04; 15,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 19,98</t>
+          <t>7,66; 19,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,46</t>
+          <t>0,82; 7,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 20,17</t>
+          <t>7,71; 20,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 16,56</t>
+          <t>1,21; 15,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,37; 22,63</t>
+          <t>12,49; 22,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,08</t>
+          <t>1,46; 6,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 15,71</t>
+          <t>7,58; 16,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 12,67</t>
+          <t>3,64; 12,62</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 13,07</t>
+          <t>1,54; 13,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 15,75</t>
+          <t>1,59; 16,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,61</t>
+          <t>0,0; 10,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,45</t>
+          <t>0,0; 7,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,49</t>
+          <t>1,41; 14,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 18,59</t>
+          <t>4,45; 18,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,73</t>
+          <t>0,79; 7,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 11,21</t>
+          <t>2,29; 11,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,81</t>
+          <t>3,0; 12,04</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,87; 27,87</t>
+          <t>11,21; 28,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,75; 30,08</t>
+          <t>12,99; 31,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,71</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,08; 46,65</t>
+          <t>25,4; 47,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,63; 27,19</t>
+          <t>10,97; 26,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,24; 33,35</t>
+          <t>14,79; 33,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,31</t>
+          <t>0,0; 6,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,28; 42,51</t>
+          <t>23,12; 43,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,24; 24,79</t>
+          <t>13,59; 24,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,16; 28,37</t>
+          <t>16,0; 28,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,18</t>
+          <t>0,57; 5,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,07; 42,77</t>
+          <t>27,08; 41,94</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,78; 17,0</t>
+          <t>7,73; 17,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,24; 22,77</t>
+          <t>12,72; 23,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 13,82</t>
+          <t>5,67; 13,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 11,85</t>
+          <t>3,95; 11,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,67; 13,95</t>
+          <t>5,65; 14,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,22; 21,41</t>
+          <t>11,1; 20,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 16,12</t>
+          <t>7,29; 15,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 14,95</t>
+          <t>5,34; 13,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 13,97</t>
+          <t>7,71; 13,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,93; 20,1</t>
+          <t>12,85; 19,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 13,49</t>
+          <t>7,65; 13,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,08; 11,59</t>
+          <t>6,04; 11,7</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,31</t>
+          <t>4,76; 11,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,11</t>
+          <t>4,03; 10,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,79; 16,97</t>
+          <t>8,65; 17,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,12; 18,22</t>
+          <t>8,08; 17,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 9,96</t>
+          <t>3,67; 9,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,3</t>
+          <t>5,24; 11,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 15,39</t>
+          <t>7,27; 15,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,88; 23,04</t>
+          <t>13,08; 23,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,52</t>
+          <t>4,97; 9,53</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 10,34</t>
+          <t>5,52; 10,62</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,13; 14,86</t>
+          <t>8,98; 14,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,97; 19,63</t>
+          <t>11,88; 19,69</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,61; 13,64</t>
+          <t>9,67; 13,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,8; 12,44</t>
+          <t>8,77; 12,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,62; 11,22</t>
+          <t>7,7; 11,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,15</t>
+          <t>7,17; 11,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,83; 11,28</t>
+          <t>7,73; 11,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,13; 12,89</t>
+          <t>9,14; 12,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,35</t>
+          <t>7,51; 11,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,86; 12,97</t>
+          <t>8,8; 13,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,07; 11,87</t>
+          <t>9,09; 11,8</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,28; 12,02</t>
+          <t>9,36; 12,03</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,15; 10,63</t>
+          <t>8,16; 10,6</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,72; 11,66</t>
+          <t>8,67; 11,63</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1833; 8598</t>
+          <t>1878; 8067</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3245; 11130</t>
+          <t>3078; 10860</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4240; 13325</t>
+          <t>4720; 13386</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3304</t>
+          <t>0; 3088</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2910; 11073</t>
+          <t>2967; 11629</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3810; 13009</t>
+          <t>3584; 12377</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>724; 7208</t>
+          <t>690; 6926</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>577; 7434</t>
+          <t>603; 6800</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5449; 15674</t>
+          <t>5942; 16180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8420; 20447</t>
+          <t>8293; 19993</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6413; 16368</t>
+          <t>6596; 17678</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>762; 7904</t>
+          <t>715; 7835</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5951; 15793</t>
+          <t>6289; 16102</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2513; 10808</t>
+          <t>2654; 11333</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7007; 17946</t>
+          <t>7327; 17873</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1520; 9341</t>
+          <t>1357; 9949</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4543; 13544</t>
+          <t>4605; 13608</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2814; 11490</t>
+          <t>3203; 11641</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8579; 20545</t>
+          <t>8920; 20773</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1119; 12208</t>
+          <t>1098; 12432</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13025; 25822</t>
+          <t>12391; 26046</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7687; 18922</t>
+          <t>7199; 18839</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18746; 34172</t>
+          <t>18993; 34590</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4298; 17716</t>
+          <t>4562; 17493</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4857; 13864</t>
+          <t>4434; 14042</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5176; 15220</t>
+          <t>5680; 15377</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2001; 8917</t>
+          <t>1552; 8527</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2803; 10652</t>
+          <t>2946; 10645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5639; 15011</t>
+          <t>5593; 14338</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8030; 18769</t>
+          <t>8359; 19099</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2808; 10140</t>
+          <t>2806; 10812</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2242; 10097</t>
+          <t>1993; 10768</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12391; 25432</t>
+          <t>12407; 24660</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15865; 29403</t>
+          <t>15699; 29926</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6463; 16502</t>
+          <t>6007; 16920</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6608; 17105</t>
+          <t>6503; 18045</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10379; 21698</t>
+          <t>11067; 22431</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>655; 6687</t>
+          <t>788; 6906</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3339; 11627</t>
+          <t>3707; 12273</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2723; 10561</t>
+          <t>2833; 10771</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6052; 15687</t>
+          <t>6017; 15291</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>639; 6036</t>
+          <t>662; 5665</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6333; 16229</t>
+          <t>6199; 16242</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1392; 12942</t>
+          <t>944; 11976</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18970; 34711</t>
+          <t>19157; 33948</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2462; 9566</t>
+          <t>2300; 9998</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11420; 24510</t>
+          <t>11829; 25403</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5695; 18790</t>
+          <t>5400; 18706</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>638; 5391</t>
+          <t>637; 5421</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>694; 6914</t>
+          <t>698; 7086</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4006</t>
+          <t>0; 3648</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3236</t>
+          <t>0; 3309</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>652; 5839</t>
+          <t>657; 6687</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2843</t>
+          <t>0; 2902</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1765; 7571</t>
+          <t>1811; 7714</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>658; 6542</t>
+          <t>667; 6108</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2200; 10165</t>
+          <t>2080; 9987</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3308</t>
+          <t>0; 3476</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2432; 8885</t>
+          <t>2258; 9058</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6091; 15623</t>
+          <t>6282; 15872</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7138; 16841</t>
+          <t>7270; 17376</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4183</t>
+          <t>0; 4403</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11579; 21538</t>
+          <t>11728; 21901</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6870; 16064</t>
+          <t>6480; 15708</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9183; 20092</t>
+          <t>8912; 20260</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4795</t>
+          <t>0; 3835</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13080; 23887</t>
+          <t>12989; 24375</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15238; 28537</t>
+          <t>15642; 28155</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18782; 32971</t>
+          <t>18591; 33376</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>633; 5800</t>
+          <t>636; 5803</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27708; 43778</t>
+          <t>27720; 42923</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10001; 21869</t>
+          <t>9944; 22563</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16863; 31380</t>
+          <t>17538; 32441</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7385; 18809</t>
+          <t>7720; 19032</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4782; 14760</t>
+          <t>4918; 14818</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7691; 18925</t>
+          <t>7663; 19053</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16135; 30782</t>
+          <t>15963; 29762</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10186; 22812</t>
+          <t>10311; 22348</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9124; 23256</t>
+          <t>8304; 21669</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20372; 36915</t>
+          <t>20383; 36966</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36418; 56607</t>
+          <t>36197; 55472</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20815; 37457</t>
+          <t>21222; 37445</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>17023; 32464</t>
+          <t>16905; 32775</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6909; 17862</t>
+          <t>7523; 18268</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7058; 17994</t>
+          <t>6521; 17240</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14298; 27590</t>
+          <t>14058; 28331</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10693; 23979</t>
+          <t>10640; 23147</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6184; 16195</t>
+          <t>5975; 15660</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9269; 20814</t>
+          <t>8862; 20293</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12516; 26027</t>
+          <t>12300; 25588</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>20194; 36120</t>
+          <t>20516; 37588</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15978; 30525</t>
+          <t>15920; 30541</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18163; 34253</t>
+          <t>18292; 35172</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30291; 49293</t>
+          <t>29808; 49154</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>34528; 56629</t>
+          <t>34268; 56782</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>65248; 92607</t>
+          <t>65682; 92845</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>61927; 87534</t>
+          <t>61693; 87705</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53124; 78190</t>
+          <t>53642; 78767</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47668; 74045</t>
+          <t>47650; 73478</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>56136; 80860</t>
+          <t>55401; 82080</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>67988; 96061</t>
+          <t>68057; 96554</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56504; 83849</t>
+          <t>55483; 82556</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>67496; 98738</t>
+          <t>67044; 99187</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>126605; 165722</t>
+          <t>126903; 164698</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>134359; 174051</t>
+          <t>135645; 174286</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116934; 152569</t>
+          <t>117201; 152216</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>124334; 166277</t>
+          <t>123542; 165872</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP26C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,5%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,32%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14,15%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 15,76</t>
+          <t>4,9; 18,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 19,19</t>
+          <t>5,77; 19,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,23; 23,33</t>
+          <t>1,07; 10,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,75; 10,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 19,79</t>
+          <t>3,64; 16,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 19,47</t>
+          <t>5,83; 20,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,74</t>
+          <t>7,8; 23,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,57</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 14,71</t>
+          <t>5,64; 14,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 16,64</t>
+          <t>6,88; 16,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,41; 14,51</t>
+          <t>5,34; 14,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,13</t>
+          <t>0,53; 6,05</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>10,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,88%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,53%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 15,85</t>
+          <t>4,13; 12,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 10,96</t>
+          <t>2,56; 9,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 17,5</t>
+          <t>7,89; 18,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,92</t>
+          <t>0,86; 9,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 12,51</t>
+          <t>6,21; 16,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 10,66</t>
+          <t>2,79; 11,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 18,95</t>
+          <t>7,29; 17,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,74</t>
+          <t>2,01; 9,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,38</t>
+          <t>6,21; 12,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,86</t>
+          <t>3,51; 8,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,97; 16,33</t>
+          <t>8,54; 15,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,91</t>
+          <t>2,24; 7,69</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12,64%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14,03%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,83%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,29%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 20,77</t>
+          <t>8,08; 21,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 22,78</t>
+          <t>11,89; 25,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 13,03</t>
+          <t>4,15; 15,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 18,27</t>
+          <t>3,3; 14,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,03; 20,57</t>
+          <t>6,64; 21,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,73; 26,8</t>
+          <t>8,33; 23,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 15,47</t>
+          <t>2,33; 13,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 16,03</t>
+          <t>5,48; 18,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,04; 17,96</t>
+          <t>9,16; 18,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 21,57</t>
+          <t>11,39; 21,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 12,5</t>
+          <t>4,24; 12,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 14,39</t>
+          <t>5,31; 13,62</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>21,3%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,05%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,78; 29,96</t>
+          <t>7,51; 20,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,05</t>
+          <t>0,8; 7,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 16,23</t>
+          <t>7,94; 20,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 15,36</t>
+          <t>1,97; 17,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 19,48</t>
+          <t>14,49; 29,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,0</t>
+          <t>1,03; 8,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 20,19</t>
+          <t>4,5; 15,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 15,33</t>
+          <t>3,87; 15,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,49; 22,13</t>
+          <t>12,48; 22,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,36</t>
+          <t>1,47; 6,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,58; 16,28</t>
+          <t>7,61; 16,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 12,62</t>
+          <t>4,02; 13,57</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,63%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>4,84%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,74%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 13,15</t>
+          <t>0,0; 7,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 16,14</t>
+          <t>1,39; 12,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,53</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4,28; 18,12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,53; 13,24</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,57; 15,87</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,57</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,62</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,41; 14,3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,35</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 18,94</t>
+          <t>0,0; 8,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,22</t>
+          <t>0,8; 7,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 11,02</t>
+          <t>2,49; 11,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 12,04</t>
+          <t>3,01; 11,02</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>18,23%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22,99%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31,49%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>18,37%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>20,49%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2,54%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35,78%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,21; 28,32</t>
+          <t>10,87; 27,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,99; 31,04</t>
+          <t>14,84; 32,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,11</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,4; 47,44</t>
+          <t>22,81; 41,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,97; 26,59</t>
+          <t>10,55; 27,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,79; 33,63</t>
+          <t>12,74; 31,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,12; 43,38</t>
+          <t>23,95; 45,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,59; 24,45</t>
+          <t>13,11; 24,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,0; 28,72</t>
+          <t>16,13; 28,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,18</t>
+          <t>0,57; 5,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,08; 41,94</t>
+          <t>25,73; 40,28</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15,46%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>11,9%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16,88%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>9,2%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,18%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,73; 17,54</t>
+          <t>5,69; 14,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,72; 23,54</t>
+          <t>11,09; 21,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,67; 13,99</t>
+          <t>7,34; 16,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 11,9</t>
+          <t>6,8; 16,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,65; 14,05</t>
+          <t>7,98; 17,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,1; 20,7</t>
+          <t>12,05; 23,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,29; 15,79</t>
+          <t>5,69; 14,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,34; 13,93</t>
+          <t>4,15; 12,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 13,99</t>
+          <t>7,62; 14,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,85; 19,7</t>
+          <t>12,92; 20,11</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,65; 13,49</t>
+          <t>7,29; 13,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,04; 11,7</t>
+          <t>6,21; 12,46</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8,42%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>7,55%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>7,0%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>12,57%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,76; 11,57</t>
+          <t>3,62; 9,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,64</t>
+          <t>5,16; 11,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,65; 17,42</t>
+          <t>7,58; 15,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,08; 17,59</t>
+          <t>13,22; 24,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,67; 9,63</t>
+          <t>4,71; 11,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,24; 11,99</t>
+          <t>3,87; 10,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,27; 15,13</t>
+          <t>8,61; 16,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,08; 23,97</t>
+          <t>8,34; 18,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,53</t>
+          <t>5,01; 9,67</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,52; 10,62</t>
+          <t>5,64; 10,46</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,98; 14,82</t>
+          <t>8,97; 14,81</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,88; 19,69</t>
+          <t>11,9; 19,13</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>11,62%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>10,41%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>9,4%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,67; 13,67</t>
+          <t>7,78; 11,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,77; 12,47</t>
+          <t>9,18; 12,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,3</t>
+          <t>7,64; 11,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,06</t>
+          <t>9,13; 13,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,73; 11,45</t>
+          <t>9,7; 13,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,14; 12,96</t>
+          <t>8,56; 12,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,18</t>
+          <t>7,59; 11,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,8; 13,02</t>
+          <t>7,78; 11,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,09; 11,8</t>
+          <t>9,31; 11,82</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,36; 12,03</t>
+          <t>9,41; 12,07</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,6</t>
+          <t>8,16; 10,68</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,63</t>
+          <t>9,2; 12,14</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5910</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7068</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2910</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2219</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4354</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6406</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>8120</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5910</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7068</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2910</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>634</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>2853</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1878; 8067</t>
+          <t>2881; 10966</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3078; 10860</t>
+          <t>3669; 12709</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4720; 13386</t>
+          <t>689; 6925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3088</t>
+          <t>478; 6448</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2967; 11629</t>
+          <t>1863; 8211</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3584; 12377</t>
+          <t>3298; 11493</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>690; 6926</t>
+          <t>4473; 13400</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>603; 6800</t>
+          <t>0; 3531</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5942; 16180</t>
+          <t>6197; 16037</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8293; 19993</t>
+          <t>8269; 20319</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6596; 17678</t>
+          <t>6504; 17392</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>715; 7835</t>
+          <t>643; 7301</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8068</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6177</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13856</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4546</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10537</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6078</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11778</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4584</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8068</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6177</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13856</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9325</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6289; 16102</t>
+          <t>4493; 13135</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2654; 11333</t>
+          <t>2800; 10629</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7327; 17873</t>
+          <t>8646; 20437</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1357; 9949</t>
+          <t>993; 11453</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4605; 13608</t>
+          <t>6308; 16319</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3203; 11641</t>
+          <t>2884; 12173</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8920; 20773</t>
+          <t>7447; 18216</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1098; 12432</t>
+          <t>1993; 9344</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12391; 26046</t>
+          <t>13057; 27305</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7199; 18839</t>
+          <t>7459; 19035</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18993; 34590</t>
+          <t>18086; 33762</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4562; 17493</t>
+          <t>4826; 16537</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9388</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12634</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5794</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4280</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8547</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>9472</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4468</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6026</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9388</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12634</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5794</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>10182</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4434; 14042</t>
+          <t>5630; 14987</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5680; 15377</t>
+          <t>8472; 18299</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1552; 8527</t>
+          <t>2903; 10832</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2946; 10645</t>
+          <t>1962; 8709</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5593; 14338</t>
+          <t>4490; 14586</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8359; 19099</t>
+          <t>5623; 15580</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2806; 10812</t>
+          <t>1526; 9093</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1993; 10768</t>
+          <t>3098; 10479</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12407; 24660</t>
+          <t>12580; 25461</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15699; 29926</t>
+          <t>15800; 29256</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6007; 16920</t>
+          <t>5740; 16524</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6503; 18045</t>
+          <t>6159; 15796</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2413</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10701</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5025</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>15949</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2664</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6846</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5849</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9945</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2413</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10701</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11089</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11067; 22431</t>
+          <t>5900; 15766</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>788; 6906</t>
+          <t>643; 5767</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3707; 12273</t>
+          <t>6385; 16602</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2833; 10771</t>
+          <t>1425; 12310</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6017; 15291</t>
+          <t>10850; 21979</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>662; 5665</t>
+          <t>788; 6604</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6199; 16242</t>
+          <t>3404; 11390</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>944; 11976</t>
+          <t>2743; 10978</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19157; 33948</t>
+          <t>19136; 34264</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2300; 9998</t>
+          <t>2307; 9761</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11829; 25403</t>
+          <t>11880; 25000</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5400; 18706</t>
+          <t>5745; 19408</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,62 +2973,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3810</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2521</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2662</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>570</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3978</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2662</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>5176</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4795</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>637; 5421</t>
+          <t>0; 3312</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>698; 7086</t>
+          <t>650; 6026</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>0; 2982</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1692; 7170</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>632; 5457</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>691; 6967</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3648</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3309</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>657; 6687</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0; 2902</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1811; 7714</t>
+          <t>0; 3076</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>667; 6108</t>
+          <t>674; 6610</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2080; 9987</t>
+          <t>2253; 10387</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3476</t>
+          <t>0; 2593</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2258; 9058</t>
+          <t>2260; 8289</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10769</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13852</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>15410</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>10300</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>11471</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1378</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>16518</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10769</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13852</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18302</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34821</t>
+          <t>31237</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6282; 15872</t>
+          <t>6420; 16127</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7270; 17376</t>
+          <t>8943; 19516</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4403</t>
+          <t>0; 3772</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11728; 21901</t>
+          <t>11165; 20410</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6480; 15708</t>
+          <t>5916; 15269</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8912; 20260</t>
+          <t>7134; 17822</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3835</t>
+          <t>0; 4778</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12989; 24375</t>
+          <t>10961; 20870</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15642; 28155</t>
+          <t>15098; 27792</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18591; 33376</t>
+          <t>18750; 33109</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>636; 5803</t>
+          <t>639; 5732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27720; 42923</t>
+          <t>24364; 38151</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>12631</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>22233</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>15823</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>14827</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>15308</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>23269</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>12515</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>9064</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>12631</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>22233</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>15823</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>24006</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9944; 22563</t>
+          <t>7718; 19039</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17538; 32441</t>
+          <t>15942; 30258</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7720; 19032</t>
+          <t>10392; 22950</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4918; 14818</t>
+          <t>9584; 23023</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7663; 19053</t>
+          <t>10266; 21884</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15963; 29762</t>
+          <t>16611; 31732</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10311; 22348</t>
+          <t>7740; 19938</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8304; 21669</t>
+          <t>5090; 15166</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20383; 36966</t>
+          <t>20140; 37243</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36197; 55472</t>
+          <t>36384; 56640</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21222; 37445</t>
+          <t>20225; 37022</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16905; 32775</t>
+          <t>16359; 32846</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>10224</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>14251</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>18260</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>28998</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>11916</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>11337</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>20433</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>15977</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>10224</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>14251</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>18260</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>44167</t>
+          <t>46404</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7523; 18268</t>
+          <t>5883; 15921</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6521; 17240</t>
+          <t>8731; 20059</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14058; 28331</t>
+          <t>12827; 25775</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10640; 23147</t>
+          <t>21072; 39827</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5975; 15660</t>
+          <t>7432; 17873</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8862; 20293</t>
+          <t>6277; 17204</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12300; 25588</t>
+          <t>14003; 26947</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>20516; 37588</t>
+          <t>11713; 25763</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15920; 30541</t>
+          <t>16062; 30993</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18292; 35172</t>
+          <t>18696; 34636</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29808; 49154</t>
+          <t>29747; 49135</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>34268; 56782</t>
+          <t>35681; 57378</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>95</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>67600</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>81283</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>79116</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>78908</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>73218</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>65539</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>59719</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>67600</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>81283</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>68652</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>60776</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>139892</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>65682; 92845</t>
+          <t>55776; 80366</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>61693; 87705</t>
+          <t>68407; 96745</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53642; 78767</t>
+          <t>56425; 82320</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47650; 73478</t>
+          <t>63956; 94496</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>55401; 82080</t>
+          <t>65895; 93971</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>68057; 96554</t>
+          <t>60202; 86826</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>55483; 82556</t>
+          <t>52926; 78613</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>67044; 99187</t>
+          <t>48839; 73096</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>126903; 164698</t>
+          <t>129891; 164954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>135645; 174286</t>
+          <t>136374; 174848</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>117201; 152216</t>
+          <t>117083; 153372</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>123542; 165872</t>
+          <t>122247; 161261</t>
         </is>
       </c>
     </row>
